--- a/data/dividends_info_20261009.xlsx
+++ b/data/dividends_info_20261009.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>46.83000183105469</v>
+        <v>46.54499816894531</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1921844896028121</v>
+        <v>0.1933612709003129</v>
       </c>
       <c r="J2" t="n">
         <v>157</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>63.5</v>
+        <v>62.15000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.102362204724409</v>
+        <v>1.126307293344995</v>
       </c>
       <c r="J3" t="n">
         <v>136</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.899999618530273</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6756756669679118</v>
       </c>
       <c r="J4" t="n">
         <v>66</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46.86999893188477</v>
+        <v>46.54499816894531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1920204865606999</v>
+        <v>0.1933612709003129</v>
       </c>
       <c r="J6" t="n">
         <v>66</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.055000066757202</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>3.746958515748678</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J7" t="n">
         <v>45</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>48.91999816894531</v>
+        <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6760016606254294</v>
+        <v>0.6748979591836735</v>
       </c>
       <c r="J8" t="n">
         <v>45</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>25.17000007629395</v>
+        <v>25.20999908447266</v>
       </c>
       <c r="I9" t="n">
-        <v>1.072705598655505</v>
+        <v>1.071003608906509</v>
       </c>
       <c r="J9" t="n">
         <v>45</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25.6299991607666</v>
+        <v>25.70999908447266</v>
       </c>
       <c r="I10" t="n">
-        <v>2.301989931014703</v>
+        <v>2.294826997315319</v>
       </c>
       <c r="J10" t="n">
         <v>45</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.19999980926514</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="I11" t="n">
-        <v>1.87500003193106</v>
+        <v>1.88172045583582</v>
       </c>
       <c r="J11" t="n">
         <v>38</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.989999771118164</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I12" t="n">
-        <v>3.338898291187508</v>
+        <v>3.327786894896843</v>
       </c>
       <c r="J12" t="n">
         <v>38</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.050000190734863</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7453415972468785</v>
+        <v>0.7407407058555365</v>
       </c>
       <c r="J14" t="n">
         <v>31</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.73999977111816</v>
+        <v>10.71000003814697</v>
       </c>
       <c r="I15" t="n">
-        <v>4.283054095001237</v>
+        <v>4.295051338576732</v>
       </c>
       <c r="J15" t="n">
         <v>17</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.659999847412109</v>
+        <v>7.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4960835607958674</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="J19" t="n">
         <v>-11</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>25.17499923706055</v>
+        <v>25.20999908447266</v>
       </c>
       <c r="I20" t="n">
-        <v>1.072492584637414</v>
+        <v>1.071003608906509</v>
       </c>
       <c r="J20" t="n">
         <v>-18</v>
@@ -1415,8 +1415,12 @@
           <t>IT0003073266</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>1.901999950408936</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.996845504004605</v>
+      </c>
       <c r="J21" t="n">
         <v>-18</v>
       </c>
@@ -1459,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>46.86999893188477</v>
+        <v>46.54499816894531</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1920204865606999</v>
+        <v>0.1933612709003129</v>
       </c>
       <c r="J22" t="n">
         <v>-18</v>
@@ -1506,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>93.40000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="I23" t="n">
-        <v>1.42398284611536</v>
+        <v>1.417155057670826</v>
       </c>
       <c r="J23" t="n">
         <v>-18</v>
@@ -1553,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.900000095367432</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I24" t="n">
-        <v>5.08474568052218</v>
+        <v>5.226481044642261</v>
       </c>
       <c r="J24" t="n">
         <v>-25</v>
@@ -3027,7 +3031,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3037,14 +3041,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3061,7 +3065,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3078,7 +3082,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3095,7 +3099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3105,7 +3109,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3252,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3265,7 +3269,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3275,14 +3279,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3292,14 +3296,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3316,7 +3320,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3333,7 +3337,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3343,14 +3347,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3360,7 +3364,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3473,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3486,7 +3490,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3513,14 +3517,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3537,7 +3541,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3571,7 +3575,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3581,14 +3585,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3598,14 +3602,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3615,14 +3619,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3632,14 +3636,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3656,7 +3660,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3666,14 +3670,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3683,14 +3687,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3707,7 +3711,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3724,7 +3728,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3741,7 +3745,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3758,7 +3762,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3775,7 +3779,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3792,7 +3796,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3809,7 +3813,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3826,7 +3830,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3843,7 +3847,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3860,7 +3864,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3877,7 +3881,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3887,14 +3891,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3911,7 +3915,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3928,7 +3932,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3938,14 +3942,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3962,7 +3966,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3979,7 +3983,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3989,14 +3993,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4006,14 +4010,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4023,14 +4027,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4040,14 +4044,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4064,7 +4068,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4081,7 +4085,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4098,7 +4102,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4115,7 +4119,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4125,14 +4129,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4142,14 +4146,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4183,7 +4187,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4210,14 +4214,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4255,61 +4259,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Redelfi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>